--- a/hall/resources/sample/VisitorBonds.xlsx
+++ b/hall/resources/sample/VisitorBonds.xlsx
@@ -50,7 +50,7 @@
     <t>list&lt;int&gt;{_}</t>
   </si>
   <si>
-    <t>map&lt;int{_}int&gt;{|}</t>
+    <t>map&lt;int{_}long&gt;{|}</t>
   </si>
   <si>
     <t>id</t>
@@ -828,15 +828,12 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1">
       <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1387,22 +1384,22 @@
       <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="D1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="E1" s="2" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="2" spans="1:5">
-      <c r="A2" s="3" t="s">
+      <c r="A2" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="B2" s="3" t="s">
+      <c r="B2" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="C2" s="3"/>
-      <c r="D2" s="3" t="s">
+      <c r="C2" s="2"/>
+      <c r="D2" s="2" t="s">
         <v>6</v>
       </c>
       <c r="E2" s="1" t="s">
@@ -1410,17 +1407,17 @@
       </c>
     </row>
     <row r="3" spans="1:5">
-      <c r="A3" s="3" t="s">
+      <c r="A3" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="B3" s="3" t="s">
+      <c r="B3" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="C3" s="3"/>
-      <c r="D3" s="3" t="s">
+      <c r="C3" s="2"/>
+      <c r="D3" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="E3" s="3" t="s">
+      <c r="E3" s="2" t="s">
         <v>11</v>
       </c>
     </row>
@@ -1432,13 +1429,13 @@
       <c r="E4" s="1"/>
     </row>
     <row r="5" spans="1:5">
-      <c r="A5" s="3">
+      <c r="A5" s="2">
         <v>1</v>
       </c>
-      <c r="B5" s="3">
+      <c r="B5" s="2">
         <v>4052001</v>
       </c>
-      <c r="C5" s="3" t="s">
+      <c r="C5" s="2" t="s">
         <v>12</v>
       </c>
       <c r="D5" s="1" t="s">
@@ -1449,13 +1446,13 @@
       </c>
     </row>
     <row r="6" spans="1:5">
-      <c r="A6" s="3">
+      <c r="A6" s="2">
         <v>2</v>
       </c>
-      <c r="B6" s="3">
+      <c r="B6" s="2">
         <v>4052002</v>
       </c>
-      <c r="C6" s="3" t="s">
+      <c r="C6" s="2" t="s">
         <v>15</v>
       </c>
       <c r="D6" s="1" t="s">
@@ -1466,13 +1463,13 @@
       </c>
     </row>
     <row r="7" spans="1:5">
-      <c r="A7" s="3">
+      <c r="A7" s="2">
         <v>3</v>
       </c>
-      <c r="B7" s="3">
+      <c r="B7" s="2">
         <v>4052003</v>
       </c>
-      <c r="C7" s="3" t="s">
+      <c r="C7" s="2" t="s">
         <v>18</v>
       </c>
       <c r="D7" s="1" t="s">
@@ -1483,13 +1480,13 @@
       </c>
     </row>
     <row r="8" spans="1:5">
-      <c r="A8" s="3">
+      <c r="A8" s="2">
         <v>4</v>
       </c>
-      <c r="B8" s="3">
+      <c r="B8" s="2">
         <v>4052004</v>
       </c>
-      <c r="C8" s="3" t="s">
+      <c r="C8" s="2" t="s">
         <v>21</v>
       </c>
       <c r="D8" s="1" t="s">
@@ -1500,13 +1497,13 @@
       </c>
     </row>
     <row r="9" spans="1:5">
-      <c r="A9" s="3">
+      <c r="A9" s="2">
         <v>5</v>
       </c>
-      <c r="B9" s="3">
+      <c r="B9" s="2">
         <v>4052005</v>
       </c>
-      <c r="C9" s="3" t="s">
+      <c r="C9" s="2" t="s">
         <v>24</v>
       </c>
       <c r="D9" s="1" t="s">
@@ -1517,13 +1514,13 @@
       </c>
     </row>
     <row r="10" spans="1:5">
-      <c r="A10" s="3">
+      <c r="A10" s="2">
         <v>6</v>
       </c>
-      <c r="B10" s="3">
+      <c r="B10" s="2">
         <v>4052006</v>
       </c>
-      <c r="C10" s="3" t="s">
+      <c r="C10" s="2" t="s">
         <v>27</v>
       </c>
       <c r="D10" s="1" t="s">
@@ -1534,13 +1531,13 @@
       </c>
     </row>
     <row r="11" spans="1:5">
-      <c r="A11" s="3">
+      <c r="A11" s="2">
         <v>7</v>
       </c>
-      <c r="B11" s="3">
+      <c r="B11" s="2">
         <v>4052007</v>
       </c>
-      <c r="C11" s="3" t="s">
+      <c r="C11" s="2" t="s">
         <v>30</v>
       </c>
       <c r="D11" s="1" t="s">
@@ -1551,13 +1548,13 @@
       </c>
     </row>
     <row r="12" spans="1:5">
-      <c r="A12" s="3">
+      <c r="A12" s="2">
         <v>8</v>
       </c>
-      <c r="B12" s="3">
+      <c r="B12" s="2">
         <v>4052008</v>
       </c>
-      <c r="C12" s="3" t="s">
+      <c r="C12" s="2" t="s">
         <v>33</v>
       </c>
       <c r="D12" s="1" t="s">
@@ -1568,13 +1565,13 @@
       </c>
     </row>
     <row r="13" spans="1:5">
-      <c r="A13" s="3">
+      <c r="A13" s="2">
         <v>9</v>
       </c>
-      <c r="B13" s="3">
+      <c r="B13" s="2">
         <v>4052009</v>
       </c>
-      <c r="C13" s="3" t="s">
+      <c r="C13" s="2" t="s">
         <v>36</v>
       </c>
       <c r="D13" s="1" t="s">
@@ -1585,13 +1582,13 @@
       </c>
     </row>
     <row r="14" spans="1:5">
-      <c r="A14" s="3">
+      <c r="A14" s="2">
         <v>10</v>
       </c>
-      <c r="B14" s="3">
+      <c r="B14" s="2">
         <v>4052010</v>
       </c>
-      <c r="C14" s="3" t="s">
+      <c r="C14" s="2" t="s">
         <v>39</v>
       </c>
       <c r="D14" s="1" t="s">
@@ -1602,13 +1599,13 @@
       </c>
     </row>
     <row r="15" spans="1:5">
-      <c r="A15" s="3">
+      <c r="A15" s="2">
         <v>11</v>
       </c>
-      <c r="B15" s="3">
+      <c r="B15" s="2">
         <v>4052011</v>
       </c>
-      <c r="C15" s="3" t="s">
+      <c r="C15" s="2" t="s">
         <v>42</v>
       </c>
       <c r="D15" s="1" t="s">
@@ -1619,13 +1616,13 @@
       </c>
     </row>
     <row r="16" spans="1:5">
-      <c r="A16" s="3">
+      <c r="A16" s="2">
         <v>12</v>
       </c>
-      <c r="B16" s="3">
+      <c r="B16" s="2">
         <v>4052012</v>
       </c>
-      <c r="C16" s="3" t="s">
+      <c r="C16" s="2" t="s">
         <v>45</v>
       </c>
       <c r="D16" s="1" t="s">
@@ -1636,13 +1633,13 @@
       </c>
     </row>
     <row r="17" spans="1:5">
-      <c r="A17" s="3">
+      <c r="A17" s="2">
         <v>13</v>
       </c>
-      <c r="B17" s="3">
+      <c r="B17" s="2">
         <v>4052013</v>
       </c>
-      <c r="C17" s="3" t="s">
+      <c r="C17" s="2" t="s">
         <v>48</v>
       </c>
       <c r="D17" s="1" t="s">
@@ -1653,13 +1650,13 @@
       </c>
     </row>
     <row r="18" spans="1:5">
-      <c r="A18" s="3">
+      <c r="A18" s="2">
         <v>14</v>
       </c>
-      <c r="B18" s="3">
+      <c r="B18" s="2">
         <v>4052014</v>
       </c>
-      <c r="C18" s="3" t="s">
+      <c r="C18" s="2" t="s">
         <v>51</v>
       </c>
       <c r="D18" s="1" t="s">
@@ -1670,13 +1667,13 @@
       </c>
     </row>
     <row r="19" spans="1:5">
-      <c r="A19" s="3">
+      <c r="A19" s="2">
         <v>15</v>
       </c>
-      <c r="B19" s="3">
+      <c r="B19" s="2">
         <v>4052015</v>
       </c>
-      <c r="C19" s="3" t="s">
+      <c r="C19" s="2" t="s">
         <v>54</v>
       </c>
       <c r="D19" s="1" t="s">
@@ -1687,25 +1684,25 @@
       </c>
     </row>
     <row r="20" spans="1:5">
-      <c r="A20" s="4"/>
-      <c r="B20" s="4"/>
-      <c r="C20" s="4"/>
-      <c r="D20" s="4"/>
-      <c r="E20" s="4"/>
+      <c r="A20" s="3"/>
+      <c r="B20" s="3"/>
+      <c r="C20" s="3"/>
+      <c r="D20" s="3"/>
+      <c r="E20" s="3"/>
     </row>
     <row r="21" spans="1:5">
-      <c r="A21" s="4"/>
-      <c r="B21" s="4"/>
-      <c r="C21" s="4"/>
-      <c r="D21" s="4"/>
-      <c r="E21" s="4"/>
+      <c r="A21" s="3"/>
+      <c r="B21" s="3"/>
+      <c r="C21" s="3"/>
+      <c r="D21" s="3"/>
+      <c r="E21" s="3"/>
     </row>
     <row r="22" spans="1:5">
-      <c r="A22" s="4"/>
-      <c r="B22" s="4"/>
-      <c r="C22" s="4"/>
-      <c r="D22" s="4"/>
-      <c r="E22" s="4"/>
+      <c r="A22" s="3"/>
+      <c r="B22" s="3"/>
+      <c r="C22" s="3"/>
+      <c r="D22" s="3"/>
+      <c r="E22" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/hall/resources/sample/VisitorBonds.xlsx
+++ b/hall/resources/sample/VisitorBonds.xlsx
@@ -1,6 +1,6 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58" uniqueCount="57">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58" uniqueCount="46">
   <si>
     <t>序号</t>
   </si>
@@ -71,7 +71,7 @@
     <t>1001_2002_3002_4002</t>
   </si>
   <si>
-    <t>1990000_15000</t>
+    <t>1980000_1000</t>
   </si>
   <si>
     <t>爆机时刻</t>
@@ -80,7 +80,7 @@
     <t>3001_4001_5002</t>
   </si>
   <si>
-    <t>1990000_16000</t>
+    <t>1980000_800</t>
   </si>
   <si>
     <t>极速漂移</t>
@@ -89,16 +89,13 @@
     <t>2001_3003_4003</t>
   </si>
   <si>
-    <t>1990000_17000</t>
-  </si>
-  <si>
     <t>全场通吃</t>
   </si>
   <si>
     <t>1002_2003_3004_4004_5003</t>
   </si>
   <si>
-    <t>1990000_18000</t>
+    <t>1980000_1500</t>
   </si>
   <si>
     <t>加倍下注</t>
@@ -107,16 +104,13 @@
     <t>2004_3005_4005</t>
   </si>
   <si>
-    <t>1990000_19000</t>
-  </si>
-  <si>
     <t>王牌荷官</t>
   </si>
   <si>
     <t>2002_4002</t>
   </si>
   <si>
-    <t>1990000_20000</t>
+    <t>1980000_500</t>
   </si>
   <si>
     <t>马戏团</t>
@@ -125,79 +119,52 @@
     <t>1003_3002_5004</t>
   </si>
   <si>
-    <t>1990000_21000</t>
-  </si>
-  <si>
     <t>科技新贵</t>
   </si>
   <si>
     <t>3006_4006</t>
   </si>
   <si>
-    <t>1990000_22000</t>
-  </si>
-  <si>
     <t>心理博弈</t>
   </si>
   <si>
     <t>4003_3003</t>
   </si>
   <si>
-    <t>1990000_23000</t>
-  </si>
-  <si>
     <t>豪门盛宴</t>
   </si>
   <si>
     <t>1004_1005</t>
   </si>
   <si>
-    <t>1990000_24000</t>
-  </si>
-  <si>
     <t>都市传说</t>
   </si>
   <si>
     <t>4004_5005</t>
   </si>
   <si>
-    <t>1990000_25000</t>
-  </si>
-  <si>
     <t>幸运联盟</t>
   </si>
   <si>
     <t>1006_2006_3006</t>
   </si>
   <si>
-    <t>1990000_26000</t>
-  </si>
-  <si>
     <t>至尊VIP厅</t>
   </si>
   <si>
     <t>5001_5002_5006</t>
   </si>
   <si>
-    <t>1990000_27000</t>
-  </si>
-  <si>
     <t>51区档案</t>
   </si>
   <si>
     <t>3004_5003</t>
   </si>
   <si>
-    <t>1990000_28000</t>
-  </si>
-  <si>
     <t>24小时营业</t>
   </si>
   <si>
     <t>1001_2001_2005_3001</t>
-  </si>
-  <si>
-    <t>1990000_29000</t>
   </si>
 </sst>
 </file>
@@ -1476,7 +1443,7 @@
         <v>19</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
     </row>
     <row r="8" spans="1:5">
@@ -1487,13 +1454,13 @@
         <v>4052004</v>
       </c>
       <c r="C8" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="D8" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="D8" s="1" t="s">
+      <c r="E8" s="1" t="s">
         <v>22</v>
-      </c>
-      <c r="E8" s="1" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="9" spans="1:5">
@@ -1504,13 +1471,13 @@
         <v>4052005</v>
       </c>
       <c r="C9" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="D9" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="D9" s="1" t="s">
-        <v>25</v>
-      </c>
       <c r="E9" s="1" t="s">
-        <v>26</v>
+        <v>17</v>
       </c>
     </row>
     <row r="10" spans="1:5">
@@ -1521,13 +1488,13 @@
         <v>4052006</v>
       </c>
       <c r="C10" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="D10" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="E10" s="1" t="s">
         <v>27</v>
-      </c>
-      <c r="D10" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="E10" s="1" t="s">
-        <v>29</v>
       </c>
     </row>
     <row r="11" spans="1:5">
@@ -1538,13 +1505,13 @@
         <v>4052007</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>32</v>
+        <v>17</v>
       </c>
     </row>
     <row r="12" spans="1:5">
@@ -1555,13 +1522,13 @@
         <v>4052008</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>35</v>
+        <v>27</v>
       </c>
     </row>
     <row r="13" spans="1:5">
@@ -1572,13 +1539,13 @@
         <v>4052009</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>38</v>
+        <v>27</v>
       </c>
     </row>
     <row r="14" spans="1:5">
@@ -1589,13 +1556,13 @@
         <v>4052010</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>41</v>
+        <v>27</v>
       </c>
     </row>
     <row r="15" spans="1:5">
@@ -1606,13 +1573,13 @@
         <v>4052011</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>44</v>
+        <v>27</v>
       </c>
     </row>
     <row r="16" spans="1:5">
@@ -1623,13 +1590,13 @@
         <v>4052012</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>46</v>
+        <v>39</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>47</v>
+        <v>17</v>
       </c>
     </row>
     <row r="17" spans="1:5">
@@ -1640,13 +1607,13 @@
         <v>4052013</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>49</v>
+        <v>41</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>50</v>
+        <v>17</v>
       </c>
     </row>
     <row r="18" spans="1:5">
@@ -1657,13 +1624,13 @@
         <v>4052014</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>51</v>
+        <v>42</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>52</v>
+        <v>43</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>53</v>
+        <v>27</v>
       </c>
     </row>
     <row r="19" spans="1:5">
@@ -1674,13 +1641,13 @@
         <v>4052015</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>54</v>
+        <v>44</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>55</v>
+        <v>45</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>56</v>
+        <v>14</v>
       </c>
     </row>
     <row r="20" spans="1:5">

--- a/hall/resources/sample/VisitorBonds.xlsx
+++ b/hall/resources/sample/VisitorBonds.xlsx
@@ -3,6 +3,11 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\gamedoc\游戏配置表\Manage\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
   <bookViews>
     <workbookView windowWidth="28800" windowHeight="12255"/>
   </bookViews>
@@ -177,10 +182,17 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="20">
+  <fonts count="21">
     <font>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
       <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -665,137 +677,137 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -804,6 +816,15 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1">
       <alignment vertical="center"/>
@@ -1075,6 +1096,11 @@
       <tableStyleElement type="pageFieldValues" dxfId="7"/>
     </tableStyle>
   </tableStyles>
+  <colors>
+    <mruColors>
+      <color rgb="00FF0000"/>
+    </mruColors>
+  </colors>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -1447,19 +1473,19 @@
       </c>
     </row>
     <row r="8" spans="1:5">
-      <c r="A8" s="2">
+      <c r="A8" s="3">
         <v>4</v>
       </c>
-      <c r="B8" s="2">
+      <c r="B8" s="3">
         <v>4052004</v>
       </c>
-      <c r="C8" s="2" t="s">
+      <c r="C8" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="D8" s="1" t="s">
+      <c r="D8" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="E8" s="1" t="s">
+      <c r="E8" s="5" t="s">
         <v>22</v>
       </c>
     </row>
@@ -1498,19 +1524,19 @@
       </c>
     </row>
     <row r="11" spans="1:5">
-      <c r="A11" s="2">
+      <c r="A11" s="3">
         <v>7</v>
       </c>
-      <c r="B11" s="2">
+      <c r="B11" s="3">
         <v>4052007</v>
       </c>
-      <c r="C11" s="2" t="s">
+      <c r="C11" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="D11" s="1" t="s">
+      <c r="D11" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="E11" s="1" t="s">
+      <c r="E11" s="5" t="s">
         <v>17</v>
       </c>
     </row>
@@ -1634,42 +1660,42 @@
       </c>
     </row>
     <row r="19" spans="1:5">
-      <c r="A19" s="2">
+      <c r="A19" s="3">
         <v>15</v>
       </c>
-      <c r="B19" s="2">
+      <c r="B19" s="3">
         <v>4052015</v>
       </c>
-      <c r="C19" s="2" t="s">
+      <c r="C19" s="4" t="s">
         <v>44</v>
       </c>
-      <c r="D19" s="1" t="s">
+      <c r="D19" s="5" t="s">
         <v>45</v>
       </c>
-      <c r="E19" s="1" t="s">
+      <c r="E19" s="5" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="20" spans="1:5">
-      <c r="A20" s="3"/>
-      <c r="B20" s="3"/>
-      <c r="C20" s="3"/>
-      <c r="D20" s="3"/>
-      <c r="E20" s="3"/>
+      <c r="A20" s="6"/>
+      <c r="B20" s="6"/>
+      <c r="C20" s="6"/>
+      <c r="D20" s="6"/>
+      <c r="E20" s="6"/>
     </row>
     <row r="21" spans="1:5">
-      <c r="A21" s="3"/>
-      <c r="B21" s="3"/>
-      <c r="C21" s="3"/>
-      <c r="D21" s="3"/>
-      <c r="E21" s="3"/>
+      <c r="A21" s="6"/>
+      <c r="B21" s="6"/>
+      <c r="C21" s="6"/>
+      <c r="D21" s="6"/>
+      <c r="E21" s="6"/>
     </row>
     <row r="22" spans="1:5">
-      <c r="A22" s="3"/>
-      <c r="B22" s="3"/>
-      <c r="C22" s="3"/>
-      <c r="D22" s="3"/>
-      <c r="E22" s="3"/>
+      <c r="A22" s="6"/>
+      <c r="B22" s="6"/>
+      <c r="C22" s="6"/>
+      <c r="D22" s="6"/>
+      <c r="E22" s="6"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/hall/resources/sample/VisitorBonds.xlsx
+++ b/hall/resources/sample/VisitorBonds.xlsx
@@ -31,8 +31,108 @@
 </workbook>
 </file>
 
+<file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <authors>
+    <author>Administrator</author>
+  </authors>
+  <commentList>
+    <comment ref="H1" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t>Administrator:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">
+模式id&amp;第X个挡位权重值加减多少值</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="I1" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t>Administrator:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">
+模式id&amp;进去此模式的权重值增加值</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="J1" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t>Administrator:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">
+Administrator:
+模式id&amp;第X个挡位-当前权重值增加或减少的值|……|第X个挡位-当前权重值增加或减少的值
+</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="K1" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t>Administrator:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">
+该数字用于仅前端显示（叠加统计）</t>
+        </r>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="90" uniqueCount="85">
   <si>
     <t>序号</t>
   </si>
@@ -46,7 +146,28 @@
     <t>成员组成</t>
   </si>
   <si>
-    <t>羁绊奖励</t>
+    <t>游戏ID</t>
+  </si>
+  <si>
+    <t>对应游戏</t>
+  </si>
+  <si>
+    <t>多语言ID</t>
+  </si>
+  <si>
+    <t>中奖概率提升（常规模式X-Y倍中奖概率提升）</t>
+  </si>
+  <si>
+    <t>进入特殊模式概率提升</t>
+  </si>
+  <si>
+    <t>特殊模式X-Y倍中奖概率提升</t>
+  </si>
+  <si>
+    <t>属性提升</t>
+  </si>
+  <si>
+    <t>备注说明</t>
   </si>
   <si>
     <t>int</t>
@@ -55,7 +176,10 @@
     <t>list&lt;int&gt;{_}</t>
   </si>
   <si>
-    <t>map&lt;int{_}long&gt;{|}</t>
+    <t>map&lt;int{,}map&lt;int{_}int&gt;{|}&gt;{;}</t>
+  </si>
+  <si>
+    <t>map&lt;int{,}int&gt;{|}</t>
   </si>
   <si>
     <t>id</t>
@@ -67,7 +191,22 @@
     <t>Members</t>
   </si>
   <si>
-    <t>Reward</t>
+    <t>gameType</t>
+  </si>
+  <si>
+    <t>languageID</t>
+  </si>
+  <si>
+    <t>winRate</t>
+  </si>
+  <si>
+    <t>specialMode</t>
+  </si>
+  <si>
+    <t>specialModeProbUp</t>
+  </si>
+  <si>
+    <t>StatBoost</t>
   </si>
   <si>
     <t>同花大顺</t>
@@ -76,7 +215,13 @@
     <t>1001_2002_3002_4002</t>
   </si>
   <si>
-    <t>1980000_1000</t>
+    <t>愤怒的小鸟</t>
+  </si>
+  <si>
+    <t>1,0_-6000</t>
+  </si>
+  <si>
+    <t>中奖概率提升3%</t>
   </si>
   <si>
     <t>爆机时刻</t>
@@ -85,7 +230,13 @@
     <t>3001_4001_5002</t>
   </si>
   <si>
-    <t>1980000_800</t>
+    <t>象财神</t>
+  </si>
+  <si>
+    <t>1,18_1000</t>
+  </si>
+  <si>
+    <t>常规模式25倍以上中奖概率提升5%</t>
   </si>
   <si>
     <t>极速漂移</t>
@@ -94,13 +245,13 @@
     <t>2001_3003_4003</t>
   </si>
   <si>
-    <t>全场通吃</t>
-  </si>
-  <si>
-    <t>1002_2003_3004_4004_5003</t>
-  </si>
-  <si>
-    <t>1980000_1500</t>
+    <t>麻将胡了</t>
+  </si>
+  <si>
+    <t>1,5_2500|6_1500</t>
+  </si>
+  <si>
+    <t>常规模式5-10倍中奖概率提升5%</t>
   </si>
   <si>
     <t>加倍下注</t>
@@ -109,19 +260,28 @@
     <t>2004_3005_4005</t>
   </si>
   <si>
+    <t>篮球巨星</t>
+  </si>
+  <si>
+    <t>1,18_400|19_200|20_200</t>
+  </si>
+  <si>
+    <t>常规模式25-50倍中奖概率提升4%</t>
+  </si>
+  <si>
     <t>王牌荷官</t>
   </si>
   <si>
     <t>2002_4002</t>
   </si>
   <si>
-    <t>1980000_500</t>
-  </si>
-  <si>
-    <t>马戏团</t>
-  </si>
-  <si>
-    <t>1003_3002_5004</t>
+    <t>绿巨人</t>
+  </si>
+  <si>
+    <t>1,12_900|14_600|16_300</t>
+  </si>
+  <si>
+    <t>常规模式10-25倍中奖概率提升3%</t>
   </si>
   <si>
     <t>科技新贵</t>
@@ -130,46 +290,103 @@
     <t>3006_4006</t>
   </si>
   <si>
+    <t>寒冰王座</t>
+  </si>
+  <si>
+    <t>1,23_400|24_200</t>
+  </si>
+  <si>
+    <t>常规模式50倍以上中奖概率提升2%</t>
+  </si>
+  <si>
     <t>心理博弈</t>
   </si>
   <si>
     <t>4003_3003</t>
   </si>
   <si>
+    <t>财神来了</t>
+  </si>
+  <si>
+    <t>2,2</t>
+  </si>
+  <si>
+    <t>触发jackpot概率提升1%</t>
+  </si>
+  <si>
     <t>豪门盛宴</t>
   </si>
   <si>
     <t>1004_1005</t>
   </si>
   <si>
+    <t>超级明星</t>
+  </si>
+  <si>
+    <t>2,25</t>
+  </si>
+  <si>
+    <t>中樱桃符号概率提升5%</t>
+  </si>
+  <si>
     <t>都市传说</t>
   </si>
   <si>
     <t>4004_5005</t>
   </si>
   <si>
+    <t>狼月</t>
+  </si>
+  <si>
+    <t>3,16</t>
+  </si>
+  <si>
+    <t>触发免费模式概率提升4%</t>
+  </si>
+  <si>
     <t>幸运联盟</t>
   </si>
   <si>
     <t>1006_2006_3006</t>
   </si>
   <si>
+    <t>宙斯vs哈迪斯</t>
+  </si>
+  <si>
+    <t>4,28_4200</t>
+  </si>
+  <si>
+    <t>免费模式50倍以上奖励概率提升3%</t>
+  </si>
+  <si>
     <t>至尊VIP厅</t>
   </si>
   <si>
     <t>5001_5002_5006</t>
   </si>
   <si>
+    <t>杰克船长</t>
+  </si>
+  <si>
+    <t>3,15</t>
+  </si>
+  <si>
+    <t>触发bonus模式概率提升5%</t>
+  </si>
+  <si>
     <t>51区档案</t>
   </si>
   <si>
     <t>3004_5003</t>
   </si>
   <si>
-    <t>24小时营业</t>
-  </si>
-  <si>
-    <t>1001_2001_2005_3001</t>
+    <t>雷神</t>
+  </si>
+  <si>
+    <t>5,29_4000</t>
+  </si>
+  <si>
+    <t>免费模式100倍以上奖励概率提升2%</t>
   </si>
 </sst>
 </file>
@@ -182,7 +399,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="21">
+  <fonts count="24">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -192,10 +409,13 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FFFF0000"/>
       <name val="宋体"/>
       <charset val="134"/>
-      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <name val="宋体"/>
+      <charset val="134"/>
     </font>
     <font>
       <u/>
@@ -341,6 +561,17 @@
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="9"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
   </fonts>
   <fills count="33">
     <fill>
@@ -536,7 +767,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="10">
+  <borders count="12">
     <border>
       <left/>
       <right/>
@@ -547,6 +778,36 @@
     <border>
       <left style="thin">
         <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color indexed="0"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="0"/>
       </left>
       <right style="thin">
         <color auto="1"/>
@@ -677,137 +938,137 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="11" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -817,13 +1078,25 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1">
@@ -1359,15 +1632,23 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E22"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="4"/>
+  <dimension ref="A1:L19"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
-    <col min="2" max="3" width="13.25" customWidth="1"/>
-    <col min="4" max="4" width="28.625" customWidth="1"/>
-    <col min="5" max="5" width="20.125" customWidth="1"/>
+    <col min="2" max="2" width="13.25" customWidth="1"/>
+    <col min="3" max="3" width="11.875" customWidth="1"/>
+    <col min="4" max="4" width="20.625" customWidth="1"/>
+    <col min="5" max="5" width="9.625" customWidth="1"/>
+    <col min="6" max="6" width="13.375" customWidth="1"/>
+    <col min="7" max="7" width="11.75" customWidth="1"/>
+    <col min="8" max="8" width="26.5" customWidth="1"/>
+    <col min="9" max="9" width="19.5" customWidth="1"/>
+    <col min="10" max="10" width="25.625" customWidth="1"/>
+    <col min="11" max="11" width="15.875" customWidth="1"/>
+    <col min="12" max="12" width="20.875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5">
+    <row r="1" spans="1:12">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1380,48 +1661,110 @@
       <c r="D1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>11</v>
+      </c>
     </row>
-    <row r="2" spans="1:5">
+    <row r="2" spans="1:12">
       <c r="A2" s="2" t="s">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="2" t="s">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>7</v>
-      </c>
+        <v>12</v>
+      </c>
+      <c r="F2" s="1"/>
+      <c r="G2" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="H2" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="I2" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="J2" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="K2" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="L2" s="1"/>
     </row>
-    <row r="3" spans="1:5">
+    <row r="3" spans="1:12">
       <c r="A3" s="2" t="s">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="C3" s="2"/>
       <c r="D3" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E3" s="2" t="s">
-        <v>11</v>
-      </c>
+        <v>18</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="F3" s="1"/>
+      <c r="G3" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="H3" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="I3" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="J3" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="K3" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="L3" s="1"/>
     </row>
-    <row r="4" spans="1:5">
+    <row r="4" spans="1:12">
       <c r="A4" s="1"/>
       <c r="B4" s="1"/>
       <c r="C4" s="1"/>
       <c r="D4" s="1"/>
       <c r="E4" s="1"/>
+      <c r="F4" s="1"/>
+      <c r="G4" s="4"/>
+      <c r="H4" s="3"/>
+      <c r="I4" s="3"/>
+      <c r="J4" s="3"/>
+      <c r="K4" s="5"/>
+      <c r="L4" s="4"/>
     </row>
-    <row r="5" spans="1:5">
+    <row r="5" ht="14.25" spans="1:12">
       <c r="A5" s="2">
         <v>1</v>
       </c>
@@ -1429,16 +1772,33 @@
         <v>4052001</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>12</v>
+        <v>25</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="E5" s="1" t="s">
-        <v>14</v>
+        <v>26</v>
+      </c>
+      <c r="E5" s="6">
+        <v>103900</v>
+      </c>
+      <c r="F5" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="G5" s="7">
+        <v>4020039</v>
+      </c>
+      <c r="H5" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="I5" s="3"/>
+      <c r="J5" s="3"/>
+      <c r="K5" s="8">
+        <v>3</v>
+      </c>
+      <c r="L5" s="4" t="s">
+        <v>29</v>
       </c>
     </row>
-    <row r="6" spans="1:5">
+    <row r="6" ht="14.25" spans="1:12">
       <c r="A6" s="2">
         <v>2</v>
       </c>
@@ -1446,16 +1806,33 @@
         <v>4052002</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="E6" s="1" t="s">
-        <v>17</v>
+        <v>31</v>
+      </c>
+      <c r="E6" s="6">
+        <v>102700</v>
+      </c>
+      <c r="F6" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="G6" s="7">
+        <v>4020113</v>
+      </c>
+      <c r="H6" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="I6" s="3"/>
+      <c r="J6" s="3"/>
+      <c r="K6" s="8">
+        <v>5</v>
+      </c>
+      <c r="L6" s="4" t="s">
+        <v>34</v>
       </c>
     </row>
-    <row r="7" spans="1:5">
+    <row r="7" ht="14.25" spans="1:12">
       <c r="A7" s="2">
         <v>3</v>
       </c>
@@ -1463,242 +1840,359 @@
         <v>4052003</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>18</v>
+        <v>35</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="E7" s="1" t="s">
-        <v>17</v>
+        <v>36</v>
+      </c>
+      <c r="E7" s="6">
+        <v>100700</v>
+      </c>
+      <c r="F7" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="G7" s="7">
+        <v>4020051</v>
+      </c>
+      <c r="H7" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="I7" s="3"/>
+      <c r="J7" s="3"/>
+      <c r="K7" s="8">
+        <v>5</v>
+      </c>
+      <c r="L7" s="4" t="s">
+        <v>39</v>
       </c>
     </row>
-    <row r="8" spans="1:5">
-      <c r="A8" s="3">
+    <row r="8" ht="14.25" spans="1:12">
+      <c r="A8" s="2">
         <v>4</v>
       </c>
-      <c r="B8" s="3">
-        <v>4052004</v>
-      </c>
-      <c r="C8" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="D8" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="E8" s="5" t="s">
-        <v>22</v>
+      <c r="B8" s="2">
+        <v>4052005</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="E8" s="6">
+        <v>101800</v>
+      </c>
+      <c r="F8" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="G8" s="7">
+        <v>4020354</v>
+      </c>
+      <c r="H8" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="I8" s="3"/>
+      <c r="J8" s="3"/>
+      <c r="K8" s="8">
+        <v>4</v>
+      </c>
+      <c r="L8" s="4" t="s">
+        <v>44</v>
       </c>
     </row>
-    <row r="9" spans="1:5">
+    <row r="9" ht="14.25" spans="1:12">
       <c r="A9" s="2">
         <v>5</v>
       </c>
       <c r="B9" s="2">
-        <v>4052005</v>
+        <v>4052006</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>23</v>
+        <v>45</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="E9" s="1" t="s">
-        <v>17</v>
+        <v>46</v>
+      </c>
+      <c r="E9" s="6">
+        <v>103100</v>
+      </c>
+      <c r="F9" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="G9" s="7">
+        <v>4020101</v>
+      </c>
+      <c r="H9" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="I9" s="3"/>
+      <c r="J9" s="3"/>
+      <c r="K9" s="8">
+        <v>3</v>
+      </c>
+      <c r="L9" s="4" t="s">
+        <v>49</v>
       </c>
     </row>
-    <row r="10" spans="1:5">
+    <row r="10" ht="14.25" spans="1:12">
       <c r="A10" s="2">
         <v>6</v>
       </c>
       <c r="B10" s="2">
-        <v>4052006</v>
+        <v>4052008</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="E10" s="1" t="s">
-        <v>27</v>
+        <v>51</v>
+      </c>
+      <c r="E10" s="6">
+        <v>102500</v>
+      </c>
+      <c r="F10" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="G10" s="7">
+        <v>4020362</v>
+      </c>
+      <c r="H10" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="I10" s="3"/>
+      <c r="J10" s="3"/>
+      <c r="K10" s="8">
+        <v>2</v>
+      </c>
+      <c r="L10" s="4" t="s">
+        <v>54</v>
       </c>
     </row>
-    <row r="11" spans="1:5">
-      <c r="A11" s="3">
+    <row r="11" ht="14.25" spans="1:12">
+      <c r="A11" s="2">
         <v>7</v>
       </c>
-      <c r="B11" s="3">
-        <v>4052007</v>
-      </c>
-      <c r="C11" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="D11" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="E11" s="5" t="s">
-        <v>17</v>
+      <c r="B11" s="2">
+        <v>4052009</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="D11" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="E11" s="6">
+        <v>101200</v>
+      </c>
+      <c r="F11" s="6" t="s">
+        <v>57</v>
+      </c>
+      <c r="G11" s="7">
+        <v>4020078</v>
+      </c>
+      <c r="H11" s="9"/>
+      <c r="I11" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="J11" s="1"/>
+      <c r="K11" s="8">
+        <v>1</v>
+      </c>
+      <c r="L11" s="4" t="s">
+        <v>59</v>
       </c>
     </row>
-    <row r="12" spans="1:5">
+    <row r="12" ht="14.25" spans="1:12">
       <c r="A12" s="2">
         <v>8</v>
       </c>
       <c r="B12" s="2">
-        <v>4052008</v>
+        <v>4052010</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>30</v>
+        <v>60</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="E12" s="1" t="s">
-        <v>27</v>
+        <v>61</v>
+      </c>
+      <c r="E12" s="6">
+        <v>100300</v>
+      </c>
+      <c r="F12" s="6" t="s">
+        <v>62</v>
+      </c>
+      <c r="G12" s="7">
+        <v>4020071</v>
+      </c>
+      <c r="H12" s="9"/>
+      <c r="I12" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="J12" s="1"/>
+      <c r="K12" s="8">
+        <v>5</v>
+      </c>
+      <c r="L12" s="4" t="s">
+        <v>64</v>
       </c>
     </row>
-    <row r="13" spans="1:5">
+    <row r="13" ht="14.25" spans="1:12">
       <c r="A13" s="2">
         <v>9</v>
       </c>
       <c r="B13" s="2">
-        <v>4052009</v>
+        <v>4052011</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>32</v>
+        <v>65</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="E13" s="1" t="s">
-        <v>27</v>
+        <v>66</v>
+      </c>
+      <c r="E13" s="6">
+        <v>101500</v>
+      </c>
+      <c r="F13" s="6" t="s">
+        <v>67</v>
+      </c>
+      <c r="G13" s="7">
+        <v>4020374</v>
+      </c>
+      <c r="H13" s="9"/>
+      <c r="I13" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="J13" s="1"/>
+      <c r="K13" s="8">
+        <v>4</v>
+      </c>
+      <c r="L13" s="4" t="s">
+        <v>69</v>
       </c>
     </row>
-    <row r="14" spans="1:5">
+    <row r="14" ht="14.25" spans="1:12">
       <c r="A14" s="2">
         <v>10</v>
       </c>
       <c r="B14" s="2">
-        <v>4052010</v>
+        <v>4052012</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>34</v>
+        <v>70</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="E14" s="1" t="s">
-        <v>27</v>
+        <v>71</v>
+      </c>
+      <c r="E14" s="6">
+        <v>102000</v>
+      </c>
+      <c r="F14" s="6" t="s">
+        <v>72</v>
+      </c>
+      <c r="G14" s="7">
+        <v>4020383</v>
+      </c>
+      <c r="H14" s="9"/>
+      <c r="I14" s="1"/>
+      <c r="J14" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="K14" s="8">
+        <v>3</v>
+      </c>
+      <c r="L14" s="4" t="s">
+        <v>74</v>
       </c>
     </row>
-    <row r="15" spans="1:5">
+    <row r="15" ht="14.25" spans="1:12">
       <c r="A15" s="2">
         <v>11</v>
       </c>
       <c r="B15" s="2">
-        <v>4052011</v>
+        <v>4052013</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>36</v>
+        <v>75</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="E15" s="1" t="s">
-        <v>27</v>
+        <v>76</v>
+      </c>
+      <c r="E15" s="6">
+        <v>102100</v>
+      </c>
+      <c r="F15" s="6" t="s">
+        <v>77</v>
+      </c>
+      <c r="G15" s="7">
+        <v>4020419</v>
+      </c>
+      <c r="H15" s="9"/>
+      <c r="I15" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="J15" s="1"/>
+      <c r="K15" s="8">
+        <v>5</v>
+      </c>
+      <c r="L15" s="4" t="s">
+        <v>79</v>
       </c>
     </row>
-    <row r="16" spans="1:5">
+    <row r="16" ht="14.25" spans="1:12">
       <c r="A16" s="2">
         <v>12</v>
       </c>
       <c r="B16" s="2">
-        <v>4052012</v>
+        <v>4052014</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>38</v>
+        <v>80</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="E16" s="1" t="s">
-        <v>17</v>
+        <v>81</v>
+      </c>
+      <c r="E16" s="6">
+        <v>102200</v>
+      </c>
+      <c r="F16" s="6" t="s">
+        <v>82</v>
+      </c>
+      <c r="G16" s="7">
+        <v>4020392</v>
+      </c>
+      <c r="H16" s="9"/>
+      <c r="I16" s="1"/>
+      <c r="J16" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="K16" s="8">
+        <v>2</v>
+      </c>
+      <c r="L16" s="4" t="s">
+        <v>84</v>
       </c>
     </row>
-    <row r="17" spans="1:5">
-      <c r="A17" s="2">
-        <v>13</v>
-      </c>
-      <c r="B17" s="2">
-        <v>4052013</v>
-      </c>
-      <c r="C17" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="D17" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="E17" s="1" t="s">
-        <v>17</v>
-      </c>
+    <row r="17" spans="1:4">
+      <c r="A17" s="10"/>
+      <c r="B17" s="10"/>
+      <c r="C17" s="10"/>
+      <c r="D17" s="10"/>
     </row>
-    <row r="18" spans="1:5">
-      <c r="A18" s="2">
-        <v>14</v>
-      </c>
-      <c r="B18" s="2">
-        <v>4052014</v>
-      </c>
-      <c r="C18" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="D18" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="E18" s="1" t="s">
-        <v>27</v>
-      </c>
+    <row r="18" spans="1:4">
+      <c r="A18" s="10"/>
+      <c r="B18" s="10"/>
+      <c r="C18" s="10"/>
+      <c r="D18" s="10"/>
     </row>
-    <row r="19" spans="1:5">
-      <c r="A19" s="3">
-        <v>15</v>
-      </c>
-      <c r="B19" s="3">
-        <v>4052015</v>
-      </c>
-      <c r="C19" s="4" t="s">
-        <v>44</v>
-      </c>
-      <c r="D19" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="E19" s="5" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5">
-      <c r="A20" s="6"/>
-      <c r="B20" s="6"/>
-      <c r="C20" s="6"/>
-      <c r="D20" s="6"/>
-      <c r="E20" s="6"/>
-    </row>
-    <row r="21" spans="1:5">
-      <c r="A21" s="6"/>
-      <c r="B21" s="6"/>
-      <c r="C21" s="6"/>
-      <c r="D21" s="6"/>
-      <c r="E21" s="6"/>
-    </row>
-    <row r="22" spans="1:5">
-      <c r="A22" s="6"/>
-      <c r="B22" s="6"/>
-      <c r="C22" s="6"/>
-      <c r="D22" s="6"/>
-      <c r="E22" s="6"/>
+    <row r="19" spans="1:4">
+      <c r="A19" s="10"/>
+      <c r="B19" s="10"/>
+      <c r="C19" s="10"/>
+      <c r="D19" s="10"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
+  <legacyDrawing r:id="rId2"/>
 </worksheet>
 </file>
--- a/hall/resources/sample/VisitorBonds.xlsx
+++ b/hall/resources/sample/VisitorBonds.xlsx
@@ -1068,7 +1068,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1088,9 +1088,6 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1783,15 +1780,15 @@
       <c r="F5" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="G5" s="7">
-        <v>4020039</v>
+      <c r="G5" s="6">
+        <v>4053105</v>
       </c>
       <c r="H5" s="3" t="s">
         <v>28</v>
       </c>
       <c r="I5" s="3"/>
       <c r="J5" s="3"/>
-      <c r="K5" s="8">
+      <c r="K5" s="7">
         <v>3</v>
       </c>
       <c r="L5" s="4" t="s">
@@ -1817,15 +1814,15 @@
       <c r="F6" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="G6" s="7">
-        <v>4020113</v>
+      <c r="G6" s="6">
+        <v>4053106</v>
       </c>
       <c r="H6" s="3" t="s">
         <v>33</v>
       </c>
       <c r="I6" s="3"/>
       <c r="J6" s="3"/>
-      <c r="K6" s="8">
+      <c r="K6" s="7">
         <v>5</v>
       </c>
       <c r="L6" s="4" t="s">
@@ -1851,15 +1848,15 @@
       <c r="F7" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="G7" s="7">
-        <v>4020051</v>
+      <c r="G7" s="6">
+        <v>4053107</v>
       </c>
       <c r="H7" s="3" t="s">
         <v>38</v>
       </c>
       <c r="I7" s="3"/>
       <c r="J7" s="3"/>
-      <c r="K7" s="8">
+      <c r="K7" s="7">
         <v>5</v>
       </c>
       <c r="L7" s="4" t="s">
@@ -1885,15 +1882,15 @@
       <c r="F8" s="6" t="s">
         <v>42</v>
       </c>
-      <c r="G8" s="7">
-        <v>4020354</v>
+      <c r="G8" s="6">
+        <v>4053108</v>
       </c>
       <c r="H8" s="3" t="s">
         <v>43</v>
       </c>
       <c r="I8" s="3"/>
       <c r="J8" s="3"/>
-      <c r="K8" s="8">
+      <c r="K8" s="7">
         <v>4</v>
       </c>
       <c r="L8" s="4" t="s">
@@ -1919,15 +1916,15 @@
       <c r="F9" s="6" t="s">
         <v>47</v>
       </c>
-      <c r="G9" s="7">
-        <v>4020101</v>
+      <c r="G9" s="6">
+        <v>4053109</v>
       </c>
       <c r="H9" s="3" t="s">
         <v>48</v>
       </c>
       <c r="I9" s="3"/>
       <c r="J9" s="3"/>
-      <c r="K9" s="8">
+      <c r="K9" s="7">
         <v>3</v>
       </c>
       <c r="L9" s="4" t="s">
@@ -1953,15 +1950,15 @@
       <c r="F10" s="6" t="s">
         <v>52</v>
       </c>
-      <c r="G10" s="7">
-        <v>4020362</v>
+      <c r="G10" s="6">
+        <v>4053110</v>
       </c>
       <c r="H10" s="3" t="s">
         <v>53</v>
       </c>
       <c r="I10" s="3"/>
       <c r="J10" s="3"/>
-      <c r="K10" s="8">
+      <c r="K10" s="7">
         <v>2</v>
       </c>
       <c r="L10" s="4" t="s">
@@ -1987,15 +1984,15 @@
       <c r="F11" s="6" t="s">
         <v>57</v>
       </c>
-      <c r="G11" s="7">
-        <v>4020078</v>
-      </c>
-      <c r="H11" s="9"/>
+      <c r="G11" s="6">
+        <v>4053111</v>
+      </c>
+      <c r="H11" s="8"/>
       <c r="I11" s="3" t="s">
         <v>58</v>
       </c>
       <c r="J11" s="1"/>
-      <c r="K11" s="8">
+      <c r="K11" s="7">
         <v>1</v>
       </c>
       <c r="L11" s="4" t="s">
@@ -2021,15 +2018,15 @@
       <c r="F12" s="6" t="s">
         <v>62</v>
       </c>
-      <c r="G12" s="7">
-        <v>4020071</v>
-      </c>
-      <c r="H12" s="9"/>
+      <c r="G12" s="6">
+        <v>4053112</v>
+      </c>
+      <c r="H12" s="8"/>
       <c r="I12" s="3" t="s">
         <v>63</v>
       </c>
       <c r="J12" s="1"/>
-      <c r="K12" s="8">
+      <c r="K12" s="7">
         <v>5</v>
       </c>
       <c r="L12" s="4" t="s">
@@ -2055,15 +2052,15 @@
       <c r="F13" s="6" t="s">
         <v>67</v>
       </c>
-      <c r="G13" s="7">
-        <v>4020374</v>
-      </c>
-      <c r="H13" s="9"/>
+      <c r="G13" s="6">
+        <v>4053113</v>
+      </c>
+      <c r="H13" s="8"/>
       <c r="I13" s="3" t="s">
         <v>68</v>
       </c>
       <c r="J13" s="1"/>
-      <c r="K13" s="8">
+      <c r="K13" s="7">
         <v>4</v>
       </c>
       <c r="L13" s="4" t="s">
@@ -2089,15 +2086,15 @@
       <c r="F14" s="6" t="s">
         <v>72</v>
       </c>
-      <c r="G14" s="7">
-        <v>4020383</v>
-      </c>
-      <c r="H14" s="9"/>
+      <c r="G14" s="6">
+        <v>4053114</v>
+      </c>
+      <c r="H14" s="8"/>
       <c r="I14" s="1"/>
       <c r="J14" s="3" t="s">
         <v>73</v>
       </c>
-      <c r="K14" s="8">
+      <c r="K14" s="7">
         <v>3</v>
       </c>
       <c r="L14" s="4" t="s">
@@ -2123,15 +2120,15 @@
       <c r="F15" s="6" t="s">
         <v>77</v>
       </c>
-      <c r="G15" s="7">
-        <v>4020419</v>
-      </c>
-      <c r="H15" s="9"/>
+      <c r="G15" s="6">
+        <v>4053115</v>
+      </c>
+      <c r="H15" s="8"/>
       <c r="I15" s="3" t="s">
         <v>78</v>
       </c>
       <c r="J15" s="1"/>
-      <c r="K15" s="8">
+      <c r="K15" s="7">
         <v>5</v>
       </c>
       <c r="L15" s="4" t="s">
@@ -2157,15 +2154,15 @@
       <c r="F16" s="6" t="s">
         <v>82</v>
       </c>
-      <c r="G16" s="7">
-        <v>4020392</v>
-      </c>
-      <c r="H16" s="9"/>
+      <c r="G16" s="6">
+        <v>4053116</v>
+      </c>
+      <c r="H16" s="8"/>
       <c r="I16" s="1"/>
       <c r="J16" s="3" t="s">
         <v>83</v>
       </c>
-      <c r="K16" s="8">
+      <c r="K16" s="7">
         <v>2</v>
       </c>
       <c r="L16" s="4" t="s">
@@ -2173,22 +2170,22 @@
       </c>
     </row>
     <row r="17" spans="1:4">
-      <c r="A17" s="10"/>
-      <c r="B17" s="10"/>
-      <c r="C17" s="10"/>
-      <c r="D17" s="10"/>
+      <c r="A17" s="9"/>
+      <c r="B17" s="9"/>
+      <c r="C17" s="9"/>
+      <c r="D17" s="9"/>
     </row>
     <row r="18" spans="1:4">
-      <c r="A18" s="10"/>
-      <c r="B18" s="10"/>
-      <c r="C18" s="10"/>
-      <c r="D18" s="10"/>
+      <c r="A18" s="9"/>
+      <c r="B18" s="9"/>
+      <c r="C18" s="9"/>
+      <c r="D18" s="9"/>
     </row>
     <row r="19" spans="1:4">
-      <c r="A19" s="10"/>
-      <c r="B19" s="10"/>
-      <c r="C19" s="10"/>
-      <c r="D19" s="10"/>
+      <c r="A19" s="9"/>
+      <c r="B19" s="9"/>
+      <c r="C19" s="9"/>
+      <c r="D19" s="9"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
